--- a/artfynd/A 57759-2025 artfynd.xlsx
+++ b/artfynd/A 57759-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820479</v>
+        <v>119820480</v>
       </c>
       <c r="B2" t="n">
-        <v>78279</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -722,7 +717,7 @@
         <v>728921</v>
       </c>
       <c r="R2" t="n">
-        <v>7209970</v>
+        <v>7209968</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,12 +784,7 @@
         <v>119820481</v>
       </c>
       <c r="B3" t="n">
-        <v>96891</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820480</v>
+        <v>119820479</v>
       </c>
       <c r="B4" t="n">
-        <v>78278</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -944,7 +929,7 @@
         <v>728921</v>
       </c>
       <c r="R4" t="n">
-        <v>7209968</v>
+        <v>7209970</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
